--- a/data/nzd0585/nzd0585.xlsx
+++ b/data/nzd0585/nzd0585.xlsx
@@ -29429,9 +29429,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0272</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -29479,9 +29485,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0151</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -29529,9 +29541,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0106</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -29579,9 +29597,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0102</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -29629,9 +29653,15 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0255</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -29679,9 +29709,15 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0159</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -29729,9 +29765,15 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0204</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -29779,9 +29821,15 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0156</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -29829,9 +29877,15 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0152</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -29879,9 +29933,15 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0152</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -29929,9 +29989,15 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0154</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -29979,9 +30045,15 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.0153</v>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -30029,9 +30101,15 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0256</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -30079,9 +30157,15 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0256</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -30129,9 +30213,15 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.0257</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -30179,9 +30269,15 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.0277</v>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -30229,9 +30325,15 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.0252</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -30279,9 +30381,15 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0314</v>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -30329,9 +30437,15 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0523</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0578</v>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -30379,9 +30493,15 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0417</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -30429,9 +30549,15 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0579</v>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -30479,9 +30605,15 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0713</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0941</v>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -30529,9 +30661,15 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0885</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -30579,9 +30717,15 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0794</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.08790000000000001</v>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -30629,9 +30773,15 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0798</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0897</v>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -30679,9 +30829,15 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0834</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0982</v>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -30729,9 +30885,15 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0743</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.0864</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -30779,9 +30941,15 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.0606</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -30829,9 +30997,15 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0887</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1354</v>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -30879,9 +31053,15 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1613</v>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -30929,9 +31109,15 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0571</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.06900000000000001</v>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -30979,9 +31165,15 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0448</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.0511</v>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -31029,9 +31221,15 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.0524</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0566</v>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -31079,9 +31277,15 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.07439999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.0867</v>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -31129,9 +31333,15 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.1497</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -31179,9 +31389,15 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1917</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -31229,9 +31445,15 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0878</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1059</v>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -31279,9 +31501,15 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.1697</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
